--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487111_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487111_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8493</v>
+        <v>3.2954</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8945</v>
+        <v>3.3139</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0452</v>
+        <v>-0.0184</v>
       </c>
       <c r="G2" t="n">
         <v>2.7105</v>
@@ -610,13 +610,13 @@
         <v>3.2811</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.1793</v>
+        <v>-1.7331</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4726</v>
+        <v>-1.0532</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7066</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.002</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6656</v>
+        <v>2.8986</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3176</v>
+        <v>2.5773</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3481</v>
+        <v>0.3213</v>
       </c>
       <c r="G3" t="n">
         <v>3.5076</v>
@@ -688,13 +688,13 @@
         <v>2.3161</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1105</v>
+        <v>-1.8775</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0708</v>
+        <v>-0.8110000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0398</v>
+        <v>-1.0665</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0825</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7203</v>
+        <v>1.3445</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3692</v>
+        <v>0.2879</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3511</v>
+        <v>1.0566</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7523</v>
@@ -766,13 +766,13 @@
         <v>3.8602</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6505</v>
+        <v>-2.0263</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.162</v>
+        <v>-1.2433</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4885</v>
+        <v>-0.783</v>
       </c>
       <c r="V4" t="n">
         <v>1.228</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4341</v>
+        <v>1.1872</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7059</v>
+        <v>2.4054</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2718</v>
+        <v>-1.2182</v>
       </c>
       <c r="G5" t="n">
         <v>2.4418</v>
@@ -844,13 +844,13 @@
         <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1078</v>
+        <v>-1.3547</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1507</v>
+        <v>-0.4511</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9571</v>
+        <v>-0.9036</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2859</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1376</v>
+        <v>0.1911</v>
       </c>
       <c r="E6" t="n">
         <v>0.2167</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.07920000000000001</v>
+        <v>-0.0256</v>
       </c>
       <c r="G6" t="n">
         <v>0.2949</v>
@@ -922,13 +922,13 @@
         <v>0.386</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5433</v>
+        <v>-0.4898</v>
       </c>
       <c r="T6" t="n">
         <v>-0.238</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3054</v>
+        <v>-0.2518</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>P. FERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3321</v>
+        <v>-0.3219</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0858</v>
+        <v>0.6005</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4179</v>
+        <v>-0.9224</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5742</v>
+        <v>-2.5786</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9574</v>
+        <v>-0.2566</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5316</v>
+        <v>-2.322</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7326</v>
+        <v>-0.2765</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6105</v>
+        <v>0.5382</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1221</v>
+        <v>-0.8147</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3068</v>
+        <v>-2.3021</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3469</v>
+        <v>-0.7948</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6537</v>
+        <v>-1.5073</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7371</v>
+        <v>2.3161</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7021</v>
+        <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7985</v>
+        <v>-0.305</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5816</v>
+        <v>-0.351</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2168</v>
+        <v>0.0459</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6965</v>
+        <v>0.2456</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8999</v>
+        <v>1.228</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5964</v>
+        <v>-0.9824000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ BLANCO</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.422</v>
+        <v>-0.6206</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7413</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1633</v>
+        <v>-0.525</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5786</v>
+        <v>-0.5742</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2566</v>
+        <v>0.9574</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.322</v>
+        <v>-1.5316</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2765</v>
+        <v>0.7326</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5382</v>
+        <v>0.6105</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8147</v>
+        <v>0.1221</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3021</v>
+        <v>-1.3068</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7948</v>
+        <v>0.3469</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5073</v>
+        <v>-1.6537</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3161</v>
+        <v>1.7371</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3161</v>
+        <v>2.7021</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4052</v>
+        <v>-1.087</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2102</v>
+        <v>-0.7631</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.195</v>
+        <v>-0.3239</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2456</v>
+        <v>-0.6965</v>
       </c>
       <c r="W8" t="n">
-        <v>1.228</v>
+        <v>0.8999</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-1.5964</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4709</v>
+        <v>-2.3707</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0219</v>
+        <v>-0.9218</v>
       </c>
       <c r="F9" t="n">
         <v>-1.4489</v>
@@ -1156,10 +1156,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.193</v>
+        <v>-0.0929</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.119</v>
+        <v>-0.0188</v>
       </c>
       <c r="U9" t="n">
         <v>-0.074</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9178</v>
+        <v>-3.7443</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6148</v>
+        <v>-2.4145</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.303</v>
+        <v>-1.3298</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2731</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7449</v>
+        <v>-0.5714</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4164</v>
+        <v>-0.2161</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3285</v>
+        <v>-0.3553</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5138</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6792</v>
+        <v>-4.2796</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5308</v>
+        <v>-3.2115</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1485</v>
+        <v>-1.0681</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6564</v>
@@ -1312,13 +1312,13 @@
         <v>2.5091</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8824</v>
+        <v>-0.4828</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0562</v>
+        <v>-0.737</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1738</v>
+        <v>0.2541</v>
       </c>
       <c r="V11" t="n">
         <v>0.2456</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.015100000000001</v>
+        <v>-2.4203</v>
       </c>
       <c r="E12" t="n">
-        <v>2.163499999999999</v>
+        <v>2.7582</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.1786</v>
+        <v>-5.178500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1926</v>
@@ -1390,13 +1390,13 @@
         <v>19.3008</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.6154</v>
+        <v>-10.0205</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.477500000000001</v>
+        <v>-5.8826</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.1379</v>
+        <v>-4.137999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8574999999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. HERRERO SANDOVAL</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2572</v>
+        <v>4.2551</v>
       </c>
       <c r="E13" t="n">
-        <v>1.624</v>
+        <v>5.738</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6332</v>
+        <v>-1.4829</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6562</v>
+        <v>4.7114</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4884</v>
+        <v>-0.9458</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1446</v>
+        <v>5.6572</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9432</v>
+        <v>6.8537</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1863</v>
+        <v>0.4968</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7569</v>
+        <v>6.3569</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.287</v>
+        <v>-2.1423</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6747</v>
+        <v>-1.4426</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3877</v>
+        <v>-0.6998</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5441</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5441</v>
+        <v>1.158</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0569</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6808</v>
+        <v>0.0423</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3761</v>
+        <v>0.7294</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7583</v>
+        <v>3.3199</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9369</v>
+        <v>3.586</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.1786</v>
+        <v>-0.266</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7114</v>
+        <v>0.7395</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9458</v>
+        <v>0.2154</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6572</v>
+        <v>0.5241</v>
       </c>
       <c r="J14" t="n">
-        <v>6.8537</v>
+        <v>1.848</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4968</v>
+        <v>1.718</v>
       </c>
       <c r="L14" t="n">
-        <v>6.3569</v>
+        <v>0.13</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1423</v>
+        <v>-1.1085</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4426</v>
+        <v>-1.5026</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6998</v>
+        <v>0.3941</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>-0.965</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R14" t="n">
-        <v>1.158</v>
+        <v>0.965</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7251</v>
+        <v>0.4756</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7588</v>
+        <v>-0.0159</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0337</v>
+        <v>0.4914</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.228</v>
+        <v>3.0699</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.6839</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>C. HERRERO SANDOVAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6785</v>
+        <v>3.2172</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1854</v>
+        <v>1.4237</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5069</v>
+        <v>1.7935</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7395</v>
+        <v>0.6562</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2154</v>
+        <v>-0.4884</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5241</v>
+        <v>1.1446</v>
       </c>
       <c r="J15" t="n">
-        <v>1.848</v>
+        <v>0.9432</v>
       </c>
       <c r="K15" t="n">
-        <v>1.718</v>
+        <v>0.1863</v>
       </c>
       <c r="L15" t="n">
-        <v>0.13</v>
+        <v>0.7569</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1085</v>
+        <v>-0.287</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5026</v>
+        <v>-0.6747</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3941</v>
+        <v>0.3877</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1659</v>
+        <v>1.0169</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4164</v>
+        <v>0.4806</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2505</v>
+        <v>0.5364</v>
       </c>
       <c r="V15" t="n">
-        <v>3.0699</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.6839</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.96</v>
+        <v>2.0529</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7244</v>
+        <v>0.9247</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2356</v>
+        <v>1.1282</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2563</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0582</v>
+        <v>1.1511</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0727</v>
+        <v>0.273</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9855</v>
+        <v>0.8781</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. DARAME PIZARRO</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3944</v>
+        <v>1.3369</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4658</v>
+        <v>1.3386</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0714</v>
+        <v>-0.0017</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9673</v>
+        <v>4.7944</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1076</v>
+        <v>1.1137</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8597</v>
+        <v>3.6808</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4281</v>
+        <v>5.7689</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0143</v>
+        <v>1.9353</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5862000000000001</v>
+        <v>3.8336</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3953</v>
+        <v>-0.9744</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1219</v>
+        <v>-0.8216</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2735</v>
+        <v>-0.1528</v>
       </c>
       <c r="P17" t="n">
-        <v>0.386</v>
+        <v>-3.8602</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-5.0182</v>
       </c>
       <c r="R17" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9756</v>
+        <v>1.0166</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0378</v>
+        <v>0.3021</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0621</v>
+        <v>0.7145</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>G. DARAME PIZARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0347</v>
+        <v>0.0008</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9651</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9174</v>
+        <v>-0.9644</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4609</v>
+        <v>-0.9673</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8093</v>
+        <v>-0.1076</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3484</v>
+        <v>-0.8597</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1421</v>
+        <v>0.4281</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6933</v>
+        <v>1.0143</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4488</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.6029</v>
+        <v>-1.3953</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5026</v>
+        <v>-1.1219</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1003</v>
+        <v>-0.2735</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1231</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.965</v>
+        <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>2.024</v>
+        <v>0.582</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3035</v>
+        <v>0.5371</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7205</v>
+        <v>0.0449</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>M. DIEYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0393</v>
+        <v>-0.3601</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3372</v>
+        <v>-1.372</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3765</v>
+        <v>1.0119</v>
       </c>
       <c r="G19" t="n">
-        <v>4.7944</v>
+        <v>-0.1377</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1137</v>
+        <v>0.5414</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6808</v>
+        <v>-0.679</v>
       </c>
       <c r="J19" t="n">
-        <v>5.7689</v>
+        <v>-0.1575</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9353</v>
+        <v>1.0557</v>
       </c>
       <c r="L19" t="n">
-        <v>3.8336</v>
+        <v>-1.2131</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9744</v>
+        <v>0.0198</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8216</v>
+        <v>-0.5143</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1528</v>
+        <v>0.5341</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.8602</v>
+        <v>-1.158</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.0182</v>
+        <v>-1.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.158</v>
+        <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3596</v>
+        <v>0.9356</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6993</v>
+        <v>0.4297</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3397</v>
+        <v>0.506</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0.2859</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8999</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DIEYE</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1727</v>
+        <v>-0.5794</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.372</v>
+        <v>0.151</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1993</v>
+        <v>-0.7304</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1377</v>
+        <v>-0.4609</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5414</v>
+        <v>-0.8093</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.679</v>
+        <v>0.3484</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1575</v>
+        <v>2.1421</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0557</v>
+        <v>0.6933</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2131</v>
+        <v>1.4488</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0198</v>
+        <v>-2.6029</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5143</v>
+        <v>-1.5026</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5341</v>
+        <v>-1.1003</v>
       </c>
       <c r="P20" t="n">
         <v>-1.158</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9301</v>
+        <v>-2.1231</v>
       </c>
       <c r="R20" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S20" t="n">
-        <v>1.123</v>
+        <v>1.4099</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4297</v>
+        <v>0.5024</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6934</v>
+        <v>0.9075</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2859</v>
+        <v>-0.3704</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6294</v>
+        <v>-2.7236</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2272</v>
+        <v>-1.3464</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5977</v>
+        <v>-1.3772</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.5399</v>
+        <v>-3.3469</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5389</v>
+        <v>-1.1685</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0011</v>
+        <v>-2.1785</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7766</v>
+        <v>-1.7591</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4753</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3013</v>
+        <v>-1.2052</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7633</v>
+        <v>-1.5878</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.0636</v>
+        <v>-0.6146</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6998</v>
+        <v>-0.9732</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.4042</v>
+        <v>-0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.9833</v>
+        <v>-1.158</v>
       </c>
       <c r="R21" t="n">
-        <v>0.579</v>
+        <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>6.0289</v>
+        <v>1.1022</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2468</v>
+        <v>0.3428</v>
       </c>
       <c r="U21" t="n">
-        <v>2.782</v>
+        <v>0.7594</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2859</v>
+        <v>-0.2859</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2264</v>
+        <v>-6.8369</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.448</v>
+        <v>-6.23</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7784</v>
+        <v>-0.6069</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3469</v>
+        <v>-4.5399</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1685</v>
+        <v>-3.5389</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1785</v>
+        <v>-1.0011</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7591</v>
+        <v>-1.7766</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-1.4753</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2052</v>
+        <v>-0.3013</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5878</v>
+        <v>-2.7633</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6146</v>
+        <v>-2.0636</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9732</v>
+        <v>-0.6998</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.193</v>
+        <v>-5.4042</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.158</v>
+        <v>-5.9833</v>
       </c>
       <c r="R22" t="n">
-        <v>0.965</v>
+        <v>0.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4006</v>
+        <v>2.8214</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7588</v>
+        <v>1.244</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3582</v>
+        <v>1.5774</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2859</v>
+        <v>0.2859</v>
       </c>
       <c r="W22" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.0153</v>
+        <v>3.682799999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>5.178599999999999</v>
+        <v>5.178699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1634</v>
+        <v>-1.4959</v>
       </c>
       <c r="G23" t="n">
-        <v>1.192500000000001</v>
+        <v>1.1925</v>
       </c>
       <c r="H23" t="n">
-        <v>-8.3468</v>
+        <v>-8.346799999999998</v>
       </c>
       <c r="I23" t="n">
         <v>9.539300000000001</v>
@@ -2224,7 +2224,7 @@
         <v>14.9425</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2074</v>
+        <v>3.207400000000002</v>
       </c>
       <c r="L23" t="n">
         <v>11.7352</v>
@@ -2245,16 +2245,16 @@
         <v>-19.3008</v>
       </c>
       <c r="R23" t="n">
-        <v>9.650099999999998</v>
+        <v>9.6501</v>
       </c>
       <c r="S23" t="n">
-        <v>10.6154</v>
+        <v>11.283</v>
       </c>
       <c r="T23" t="n">
-        <v>4.138000000000001</v>
+        <v>4.1381</v>
       </c>
       <c r="U23" t="n">
-        <v>6.4775</v>
+        <v>7.145</v>
       </c>
       <c r="V23" t="n">
         <v>0.8575000000000002</v>
